--- a/Data Cleaning and Transformation.xlsx
+++ b/Data Cleaning and Transformation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raman\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66AE445D-3365-4635-BB2C-40FB2ACB0BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038A6626-AA96-438B-B9AB-6501ADDB597B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -383,9 +383,6 @@
     <t>Casio</t>
   </si>
   <si>
-    <t>average formula use or median formula</t>
-  </si>
-  <si>
     <t>Propercase</t>
   </si>
   <si>
@@ -459,6 +456,9 @@
   </si>
   <si>
     <t>1)1</t>
+  </si>
+  <si>
+    <t>average or median functions use</t>
   </si>
 </sst>
 </file>
@@ -2395,7 +2395,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:P1000"/>
+  <dimension ref="A1:N1000"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.6640625" customWidth="1"/>
@@ -2413,7 +2413,7 @@
     <col min="17" max="17" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>19</v>
       </c>
@@ -2433,19 +2433,19 @@
         <v>24</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H1" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="I1" s="7" t="s">
-        <v>126</v>
-      </c>
       <c r="J1" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>25</v>
       </c>
@@ -2480,8 +2480,15 @@
         <f t="shared" ref="J2:J32" si="1">B2&amp;" "&amp;C2</f>
         <v>Laptop Dell</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L2" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="M2">
+        <f>COUNTBLANK(D2:D32)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>28</v>
       </c>
@@ -2518,15 +2525,11 @@
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
-      <c r="N3" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="O3">
-        <f>COUNTBLANK(D2:D32)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M3" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>32</v>
       </c>
@@ -2563,12 +2566,11 @@
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="10" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M4" s="10" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>36</v>
       </c>
@@ -2604,13 +2606,17 @@
         <v>Smartphone Samsung</v>
       </c>
       <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="10" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L5" s="10">
+        <v>2</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="N5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>38</v>
       </c>
@@ -2627,7 +2633,7 @@
         <v>20</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G6" s="16" t="str">
         <f t="shared" si="0"/>
@@ -2645,17 +2651,14 @@
         <f t="shared" si="1"/>
         <v>Backpack North Face</v>
       </c>
-      <c r="N6" s="10">
-        <v>2</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="P6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L6" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>41</v>
       </c>
@@ -2688,14 +2691,14 @@
         <f t="shared" si="1"/>
         <v>Headphones Sony</v>
       </c>
-      <c r="N7" s="9" t="s">
+      <c r="L7" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="M7" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="O7" s="9" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>45</v>
       </c>
@@ -2730,14 +2733,14 @@
         <f t="shared" si="1"/>
         <v>T-shirt Adidas</v>
       </c>
-      <c r="N8" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="O8" s="10" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L8" s="9">
+        <v>2</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>48</v>
       </c>
@@ -2772,14 +2775,11 @@
         <f t="shared" si="1"/>
         <v>Blender Ninja</v>
       </c>
-      <c r="N9" s="9">
-        <v>2</v>
-      </c>
-      <c r="O9" s="10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M9" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>51</v>
       </c>
@@ -2814,11 +2814,14 @@
         <f t="shared" si="1"/>
         <v>Tablet Apple</v>
       </c>
-      <c r="O10" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L10">
+        <v>3</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>54</v>
       </c>
@@ -2853,14 +2856,11 @@
         <f t="shared" si="1"/>
         <v>Hiking Boots Timberland</v>
       </c>
-      <c r="N11">
-        <v>3</v>
-      </c>
-      <c r="O11" s="10" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M11" s="10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>58</v>
       </c>
@@ -2895,11 +2895,14 @@
         <f t="shared" si="1"/>
         <v>Laptop HP</v>
       </c>
-      <c r="O12" s="10" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L12" t="s">
+        <v>121</v>
+      </c>
+      <c r="M12" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>61</v>
       </c>
@@ -2934,14 +2937,14 @@
         <f t="shared" si="1"/>
         <v>Sneakers Adidas</v>
       </c>
-      <c r="N13" t="s">
-        <v>122</v>
-      </c>
-      <c r="O13" s="10" t="s">
+      <c r="L13" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M13" s="10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>62</v>
       </c>
@@ -2976,14 +2979,11 @@
         <f t="shared" si="1"/>
         <v>Coffee Maker Nespresso</v>
       </c>
-      <c r="N14" t="s">
-        <v>124</v>
-      </c>
-      <c r="O14" s="10" t="s">
+      <c r="M14" s="10" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>64</v>
       </c>
@@ -3018,11 +3018,14 @@
         <f t="shared" si="1"/>
         <v>Smartwatch Fitbit</v>
       </c>
-      <c r="O15" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L15" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>67</v>
       </c>
@@ -3057,14 +3060,8 @@
         <f t="shared" si="1"/>
         <v>headphones Bose</v>
       </c>
-      <c r="N16" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="O16" s="10" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>70</v>
       </c>
@@ -3099,8 +3096,14 @@
         <f t="shared" si="1"/>
         <v>Laptop Bag Samsonite</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L17" t="s">
+        <v>130</v>
+      </c>
+      <c r="M17" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>74</v>
       </c>
@@ -3135,14 +3138,14 @@
         <f t="shared" si="1"/>
         <v>Smartwatch Huawei</v>
       </c>
-      <c r="N18" t="s">
-        <v>131</v>
-      </c>
-      <c r="O18" s="10" t="s">
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18" s="10" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>76</v>
       </c>
@@ -3177,14 +3180,8 @@
         <f t="shared" si="1"/>
         <v>Laptop Asus</v>
       </c>
-      <c r="N19">
-        <v>2</v>
-      </c>
-      <c r="O19" s="10" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>78</v>
       </c>
@@ -3220,7 +3217,7 @@
         <v>Sunglasses Oakley</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>81</v>
       </c>
@@ -3254,7 +3251,7 @@
         <v>Camping Tent Coleman</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>84</v>
       </c>
@@ -3290,7 +3287,7 @@
         <v>Camera Nikon</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>87</v>
       </c>
@@ -3326,7 +3323,7 @@
         <v>Microwave Panasonic</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>90</v>
       </c>
@@ -3362,7 +3359,7 @@
         <v>Fitness Tracker Xiaomi</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>93</v>
       </c>
@@ -3398,7 +3395,7 @@
         <v>Smartphone Google</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>96</v>
       </c>
@@ -3432,7 +3429,7 @@
         <v>Sunglasses Ray-Ban</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>98</v>
       </c>
@@ -3468,7 +3465,7 @@
         <v>Blender Vitamix</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>100</v>
       </c>
@@ -3504,7 +3501,7 @@
         <v>Dress Zara</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>103</v>
       </c>
@@ -3540,7 +3537,7 @@
         <v>Toaster Hamilton</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>106</v>
       </c>
@@ -3576,7 +3573,7 @@
         <v>Fitness Tracker Garmin</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>108</v>
       </c>
@@ -3612,7 +3609,7 @@
         <v>Jeans Levi's</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>111</v>
       </c>
